--- a/tests/agent_contract/data/R1_finance_ledger.xlsx
+++ b/tests/agent_contract/data/R1_finance_ledger.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G183"/>
+  <dimension ref="A1:G179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,74 +456,74 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>9135</t>
+          <t>4587</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>管理费用11</t>
+          <t>现金2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>管理费用</t>
+          <t>现金</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>成本</t>
+          <t>资产</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1518.79</v>
+        <v>47684.79</v>
       </c>
       <c r="F2" t="n">
-        <v>47441.14</v>
+        <v>44533.11</v>
       </c>
       <c r="G2" t="n">
-        <v>-45922.35</v>
+        <v>656.51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3816</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>现金12</t>
+          <t>应付账款12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>现金</t>
+          <t>应付账款</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>资产</t>
+          <t>负债</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3729.15</v>
+        <v>29780.55</v>
       </c>
       <c r="F3" t="n">
-        <v>9774.33</v>
+        <v>45805.41</v>
       </c>
       <c r="G3" t="n">
-        <v>-6045.18</v>
+        <v>-16024.86</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5240</t>
+          <t>7191</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>盈余公积2</t>
+          <t>盈余公积8</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -537,148 +537,145 @@
         </is>
       </c>
       <c r="E4" t="n">
+        <v>7407.55</v>
+      </c>
+      <c r="F4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" t="n">
-        <v>13495.67</v>
-      </c>
       <c r="G4" t="n">
-        <v>-13495.67</v>
+        <v>7407.55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6951</t>
+          <t>7169</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>管理费用2</t>
+          <t>投资收益4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>管理费用</t>
+          <t>投资收益</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>成本</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>5451.14</v>
+          <t>损益</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>7029.59</v>
+        <v>20621.2</v>
       </c>
       <c r="G5" t="n">
-        <v>-1578.45</v>
+        <v>-7464.050000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7706</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>固定资产9</t>
+          <t>盈余公积4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>固定资产</t>
+          <t>盈余公积</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>资产</t>
+          <t>权益</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>35278.88</v>
+        <v>33004.71</v>
       </c>
       <c r="F6" t="n">
-        <v>13158.06</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>22120.82</v>
+        <v>33004.71</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8763</t>
+          <t>8116</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>应付账款4</t>
+          <t>主营业务收入4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>应付账款</t>
+          <t>主营业务收入</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>负债</t>
+          <t>损益</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>48283.36</v>
       </c>
       <c r="F7" t="n">
-        <v>19599.67</v>
+        <v>15306.7</v>
       </c>
       <c r="G7" t="n">
-        <v>-19599.67</v>
+        <v>32976.66</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>8507</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>银行存款7</t>
+          <t>长期借款5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>银行存款</t>
+          <t>长期借款</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>资产</t>
+          <t>负债</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>23070.74</v>
+        <v>23693.1</v>
       </c>
       <c r="F8" t="n">
-        <v>23116.84</v>
+        <v>22102.34</v>
       </c>
       <c r="G8" t="n">
-        <v>-46.09999999999854</v>
+        <v>1590.759999999998</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>主营业务收入8</t>
+          <t>主营业务收入3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -691,27 +688,30 @@
           <t>损益</t>
         </is>
       </c>
+      <c r="E9" t="n">
+        <v>23239.02</v>
+      </c>
       <c r="F9" t="n">
-        <v>38367.74</v>
+        <v>47234.11</v>
       </c>
       <c r="G9" t="n">
-        <v>-8493.119999999999</v>
+        <v>-23995.09</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9139</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>固定资产5</t>
+          <t>现金3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>固定资产</t>
+          <t>现金</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -720,355 +720,364 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>25267.88</v>
       </c>
       <c r="G10" t="n">
-        <v>19905.64</v>
+        <v>-22419.15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5376</t>
+          <t>6318</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>现金4</t>
+          <t>投资收益2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>现金</t>
+          <t>投资收益</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>资产</t>
+          <t>损益</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>16337.35</v>
+        <v>4959.01</v>
       </c>
       <c r="F11" t="n">
-        <v>14439.21</v>
+        <v>10407.83</v>
       </c>
       <c r="G11" t="n">
-        <v>1898.140000000001</v>
+        <v>-5448.82</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>9178</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>主营业务收入14</t>
+          <t>短期借款6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>主营业务收入</t>
+          <t>短期借款</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>损益</t>
-        </is>
+          <t>负债</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>41244.97</v>
       </c>
       <c r="F12" t="n">
-        <v>42269.35</v>
+        <v>6355.32</v>
       </c>
       <c r="G12" t="n">
-        <v>-26151.14</v>
+        <v>34889.65</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3259</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>应付账款5</t>
+          <t>管理费用9</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>应付账款</t>
+          <t>管理费用</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>负债</t>
-        </is>
+          <t>成本</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>23581.89</v>
       </c>
       <c r="F13" t="n">
-        <v>10974.45</v>
+        <v>5456.19</v>
       </c>
       <c r="G13" t="n">
-        <v>12285.37</v>
+        <v>18125.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>8885</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>固定资产8</t>
+          <t>主营业务成本2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>固定资产</t>
+          <t>主营业务成本</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>资产</t>
+          <t>成本</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>27918.14</v>
+        <v>8157.32</v>
       </c>
       <c r="F14" t="n">
-        <v>23868.81</v>
+        <v>20432.83</v>
       </c>
       <c r="G14" t="n">
-        <v>4049.329999999998</v>
+        <v>-12275.51</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>4805</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>固定资产13</t>
+          <t>主营业务成本1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>固定资产</t>
+          <t>主营业务成本</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>资产</t>
-        </is>
+          <t>成本</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>43987.3</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>27882.12</v>
+        <v>43987.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6449</t>
+          <t>8862</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>固定资产7</t>
+          <t>盈余公积10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>固定资产</t>
+          <t>盈余公积</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>资产</t>
+          <t>权益</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1539.02</v>
+        <v>18841.01</v>
       </c>
       <c r="F16" t="n">
-        <v>16822.19</v>
+        <v>11621.02</v>
       </c>
       <c r="G16" t="n">
-        <v>-15283.17</v>
+        <v>7219.989999999998</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6849</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>现金1</t>
+          <t>主营业务成本14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>现金</t>
+          <t>主营业务成本</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>资产</t>
+          <t>成本</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5308.88</v>
+        <v>41091.03</v>
       </c>
       <c r="F17" t="n">
-        <v>9644.91</v>
+        <v>12466.42</v>
       </c>
       <c r="G17" t="n">
-        <v>-4336.03</v>
+        <v>28624.61</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>7551</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>长期借款6</t>
+          <t>管理费用4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>长期借款</t>
+          <t>管理费用</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>负债</t>
+          <t>成本</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>6789.83</v>
       </c>
       <c r="F18" t="n">
-        <v>32348.91</v>
+        <v>11005.64</v>
       </c>
       <c r="G18" t="n">
-        <v>-32348.91</v>
+        <v>-4215.809999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>6328</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>长期借款8</t>
+          <t>主营业务收入6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>长期借款</t>
+          <t>主营业务收入</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>负债</t>
+          <t>损益</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8804.4</v>
+        <v>27434.32</v>
       </c>
       <c r="F19" t="n">
-        <v>5098.94</v>
+        <v>1907.9</v>
       </c>
       <c r="G19" t="n">
-        <v>3705.46</v>
+        <v>25526.42</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>6353</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>长期借款1</t>
+          <t>存货5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>长期借款</t>
+          <t>存货</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>负债</t>
+          <t>资产</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>17913.66</v>
+        <v>31452.26</v>
       </c>
       <c r="G20" t="n">
-        <v>-1850.82</v>
+        <v>-20363.65</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2853</t>
+          <t>3199</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>主营业务成本3</t>
+          <t>银行存款10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>主营业务成本</t>
+          <t>银行存款</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>成本</t>
+          <t>资产</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>9820.82</v>
+        <v>11514.89</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>28672.73</v>
       </c>
       <c r="G21" t="n">
-        <v>9820.82</v>
+        <v>-17157.84</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4206</t>
+          <t>5450</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>应收账款12</t>
+          <t>存货3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>应收账款</t>
+          <t>存货</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1077,122 +1086,122 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>26650.69</v>
+        <v>25341.37</v>
       </c>
       <c r="F22" t="n">
-        <v>6856.81</v>
+        <v>17985.52</v>
       </c>
       <c r="G22" t="n">
-        <v>19793.88</v>
+        <v>7355.849999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7970</t>
+          <t>7360</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>投资收益7</t>
+          <t>实收资本1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>投资收益</t>
+          <t>实收资本</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>损益</t>
+          <t>权益</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>11004.93</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>39661.25</v>
+        <v>22250.31</v>
       </c>
       <c r="G23" t="n">
-        <v>-28656.32</v>
+        <v>-22250.31</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9466</t>
+          <t>5938</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>投资收益10</t>
+          <t>应付账款9</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>投资收益</t>
+          <t>应付账款</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>损益</t>
+          <t>负债</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>29537.72</v>
+        <v>44347.66</v>
       </c>
       <c r="F24" t="n">
-        <v>12044.05</v>
+        <v>28250.44</v>
       </c>
       <c r="G24" t="n">
-        <v>17493.67</v>
+        <v>16097.22</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5095</t>
+          <t>9627</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>盈余公积5</t>
+          <t>长期借款11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>盈余公积</t>
+          <t>长期借款</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>权益</t>
+          <t>负债</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6020.89</v>
+        <v>27261.89</v>
       </c>
       <c r="F25" t="n">
-        <v>13128.07</v>
+        <v>36171.56</v>
       </c>
       <c r="G25" t="n">
-        <v>-7107.179999999999</v>
+        <v>-8909.669999999998</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9906</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>短期借款5</t>
+          <t>应付账款13</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>短期借款</t>
+          <t>应付账款</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1201,153 +1210,153 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>39902.49</v>
+        <v>12517.16</v>
       </c>
       <c r="F26" t="n">
-        <v>32039.32</v>
+        <v>39224.3</v>
       </c>
       <c r="G26" t="n">
-        <v>7863.169999999998</v>
+        <v>-26707.14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>盈余公积14</t>
+          <t>主营业务收入9</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>盈余公积</t>
+          <t>主营业务收入</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>权益</t>
+          <t>损益</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>17413.86</v>
+        <v>49499.4</v>
       </c>
       <c r="F27" t="n">
-        <v>11207.92</v>
+        <v>41328.32</v>
       </c>
       <c r="G27" t="n">
-        <v>6205.940000000001</v>
+        <v>8171.080000000002</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3564</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>主营业务成本1</t>
+          <t>应付账款7</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>主营业务成本</t>
+          <t>应付账款</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>成本</t>
+          <t>负债</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2742.59</v>
+        <v>40326.28</v>
       </c>
       <c r="F28" t="n">
-        <v>15034.73</v>
+        <v>10494.8</v>
       </c>
       <c r="G28" t="n">
-        <v>-12292.14</v>
+        <v>29831.48</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>5833</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>银行存款8</t>
+          <t>管理费用14</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>银行存款</t>
+          <t>管理费用</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>资产</t>
+          <t>成本</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>8928.23</v>
+        <v>16565.01</v>
       </c>
       <c r="F29" t="n">
-        <v>35643.87</v>
+        <v>4746.08</v>
       </c>
       <c r="G29" t="n">
-        <v>-26715.64</v>
+        <v>11818.93</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5266</t>
+          <t>8385</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>投资收益9</t>
+          <t>管理费用7</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>投资收益</t>
+          <t>管理费用</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>损益</t>
+          <t>成本</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>24446.52</v>
+        <v>39494.72</v>
       </c>
       <c r="F30" t="n">
-        <v>45341.5</v>
+        <v>39372.24</v>
       </c>
       <c r="G30" t="n">
-        <v>-20894.98</v>
+        <v>122.4800000000032</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>3695</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>固定资产11</t>
+          <t>存货9</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>固定资产</t>
+          <t>存货</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1356,83 +1365,80 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>10052.23</v>
+        <v>2219.01</v>
       </c>
       <c r="G31" t="n">
-        <v>13225.69</v>
+        <v>38423.64</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>7920</t>
+          <t>6986</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>主营业务收入12</t>
+          <t>实收资本10</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>主营业务收入</t>
+          <t>实收资本</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>损益</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>24871.43</v>
+          <t>权益</t>
+        </is>
       </c>
       <c r="F32" t="n">
-        <v>38361.09</v>
+        <v>24484.32</v>
       </c>
       <c r="G32" t="n">
-        <v>-13489.66</v>
+        <v>-18139.6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>7797</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>应收账款7</t>
+          <t>管理费用15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>应收账款</t>
+          <t>管理费用</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>资产</t>
+          <t>成本</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>11131.06</v>
+        <v>41881.06</v>
       </c>
       <c r="F33" t="n">
-        <v>14913.96</v>
+        <v>6040.1</v>
       </c>
       <c r="G33" t="n">
-        <v>-3782.9</v>
+        <v>35840.96</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4663</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>盈余公积10</t>
+          <t>盈余公积9</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1446,60 +1452,60 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>34827.05</v>
+        <v>29542.7</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>34330.06</v>
       </c>
       <c r="G34" t="n">
-        <v>34827.05</v>
+        <v>-4787.359999999997</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>主营业务收入1</t>
+          <t>主营业务成本10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>主营业务收入</t>
+          <t>主营业务成本</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>损益</t>
+          <t>成本</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>44062.18</v>
+        <v>24828.6</v>
       </c>
       <c r="F35" t="n">
-        <v>17743.82</v>
+        <v>10321.57</v>
       </c>
       <c r="G35" t="n">
-        <v>26318.36</v>
+        <v>14507.03</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>1468</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>银行存款3</t>
+          <t>现金9</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>银行存款</t>
+          <t>现金</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1508,29 +1514,29 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>22529.65</v>
+        <v>44793.39</v>
       </c>
       <c r="F36" t="n">
-        <v>12286.4</v>
+        <v>39269.98</v>
       </c>
       <c r="G36" t="n">
-        <v>10243.25</v>
+        <v>5523.409999999996</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2950</t>
+          <t>9159</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>存货7</t>
+          <t>银行存款2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>存货</t>
+          <t>银行存款</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1539,145 +1545,145 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>14745.25</v>
+        <v>11411.14</v>
       </c>
       <c r="F37" t="n">
-        <v>3111.43</v>
+        <v>45081.46</v>
       </c>
       <c r="G37" t="n">
-        <v>11633.82</v>
+        <v>-33670.32</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>7696</t>
+          <t>6125</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>银行存款2</t>
+          <t>盈余公积2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>银行存款</t>
+          <t>盈余公积</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>资产</t>
+          <t>权益</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>11895.3</v>
+        <v>12159.62</v>
       </c>
       <c r="F38" t="n">
-        <v>9992.639999999999</v>
+        <v>11074.84</v>
       </c>
       <c r="G38" t="n">
-        <v>1902.66</v>
+        <v>1084.780000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2516</t>
+          <t>3150</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>管理费用8</t>
+          <t>主营业务收入13</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>管理费用</t>
+          <t>主营业务收入</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>成本</t>
+          <t>损益</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>14117.87</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>15408.38</v>
+        <v>35035.2</v>
       </c>
       <c r="G39" t="n">
-        <v>-1290.509999999998</v>
+        <v>-35035.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6484</t>
+          <t>6821</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>管理费用6</t>
+          <t>固定资产5</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>管理费用</t>
+          <t>固定资产</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>成本</t>
-        </is>
+          <t>资产</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5848.26</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>45090.81</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>-39242.55</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2957</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>主营业务成本9</t>
+          <t>应收账款14</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>主营业务成本</t>
+          <t>应收账款</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>成本</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>39663.48</v>
+          <t>资产</t>
+        </is>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>33661.24</v>
       </c>
       <c r="G41" t="n">
-        <v>39663.48</v>
+        <v>-6982.989999999998</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>实收资本2</t>
+          <t>实收资本4</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1690,87 +1696,84 @@
           <t>权益</t>
         </is>
       </c>
-      <c r="E42" t="n">
-        <v>13310.29</v>
-      </c>
       <c r="F42" t="n">
-        <v>24396.18</v>
+        <v>30847.42</v>
       </c>
       <c r="G42" t="n">
-        <v>-11085.89</v>
+        <v>-8053.169999999998</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>7152</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>主营业务成本4</t>
+          <t>实收资本8</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>主营业务成本</t>
+          <t>实收资本</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>成本</t>
+          <t>权益</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>29131.41</v>
+        <v>2102.52</v>
       </c>
       <c r="F43" t="n">
-        <v>44119.87</v>
+        <v>2241.72</v>
       </c>
       <c r="G43" t="n">
-        <v>-14988.46</v>
+        <v>-139.1999999999998</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2350</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>短期借款2</t>
+          <t>固定资产1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>短期借款</t>
+          <t>固定资产</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>负债</t>
+          <t>资产</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>44718.7</v>
+        <v>26210.82</v>
       </c>
       <c r="F44" t="n">
-        <v>28373.4</v>
+        <v>7095.24</v>
       </c>
       <c r="G44" t="n">
-        <v>16345.3</v>
+        <v>19115.58</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6606</t>
+          <t>9579</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>应收账款11</t>
+          <t>应收账款1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1784,150 +1787,153 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>48551.15</v>
+        <v>45274.56</v>
       </c>
       <c r="F45" t="n">
-        <v>40786.66</v>
+        <v>34146.27</v>
       </c>
       <c r="G45" t="n">
-        <v>7764.489999999998</v>
+        <v>11128.29</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>8258</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>应付账款6</t>
+          <t>固定资产10</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>应付账款</t>
+          <t>固定资产</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>负债</t>
-        </is>
+          <t>资产</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>38459.69</v>
       </c>
       <c r="F46" t="n">
-        <v>29468.14</v>
+        <v>15038.24</v>
       </c>
       <c r="G46" t="n">
-        <v>16221.8</v>
+        <v>23421.45</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6984</t>
+          <t>7033</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>主营业务收入9</t>
+          <t>固定资产2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>主营业务收入</t>
+          <t>固定资产</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>损益</t>
+          <t>资产</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1094.04</v>
+        <v>31614.58</v>
       </c>
       <c r="F47" t="n">
-        <v>39721.45</v>
+        <v>44238.32</v>
       </c>
       <c r="G47" t="n">
-        <v>-38627.41</v>
+        <v>-12623.74</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>7010</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>实收资本8</t>
+          <t>短期借款4</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>实收资本</t>
+          <t>短期借款</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>权益</t>
+          <t>负债</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>17067.15</v>
+        <v>24547.66</v>
       </c>
       <c r="F48" t="n">
-        <v>43048.72</v>
+        <v>7341.82</v>
       </c>
       <c r="G48" t="n">
-        <v>-25981.57</v>
+        <v>17205.84</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>9956</t>
+          <t>5864</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>固定资产14</t>
+          <t>投资收益11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>固定资产</t>
+          <t>投资收益</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>资产</t>
+          <t>损益</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>42560.07</v>
+        <v>11757.97</v>
       </c>
       <c r="F49" t="n">
-        <v>4895.76</v>
+        <v>46374.32</v>
       </c>
       <c r="G49" t="n">
-        <v>37664.31</v>
+        <v>-34616.35</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2239</t>
+          <t>4333</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>实收资本11</t>
+          <t>盈余公积13</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>实收资本</t>
+          <t>盈余公积</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1935,114 +1941,123 @@
           <t>权益</t>
         </is>
       </c>
+      <c r="E50" t="n">
+        <v>46204.68</v>
+      </c>
       <c r="F50" t="n">
-        <v>19968.75</v>
+        <v>4967.28</v>
       </c>
       <c r="G50" t="n">
-        <v>15557.92</v>
+        <v>41237.4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>9382</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>固定资产6</t>
+          <t>长期借款10</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>固定资产</t>
+          <t>长期借款</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>资产</t>
-        </is>
+          <t>负债</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>39868.68</v>
       </c>
       <c r="F51" t="n">
-        <v>26073.73</v>
+        <v>26053.58</v>
       </c>
       <c r="G51" t="n">
-        <v>17546.94</v>
+        <v>13815.1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>7672</t>
+          <t>2821</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>短期借款1</t>
+          <t>实收资本11</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>短期借款</t>
+          <t>实收资本</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>负债</t>
+          <t>权益</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>39276.77</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>42338.14</v>
+        <v>7975.22</v>
       </c>
       <c r="G52" t="n">
-        <v>-3061.370000000003</v>
+        <v>-7975.22</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>8519</t>
+          <t>4087</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>银行存款12</t>
+          <t>投资收益8</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>银行存款</t>
+          <t>投资收益</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>资产</t>
-        </is>
+          <t>损益</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>20137.69</v>
       </c>
       <c r="F53" t="n">
-        <v>22514.68</v>
+        <v>16712.16</v>
       </c>
       <c r="G53" t="n">
-        <v>-22514.68</v>
+        <v>3425.529999999999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>投资收益6</t>
+          <t>主营业务收入7</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>投资收益</t>
+          <t>主营业务收入</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2051,91 +2066,91 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>41571.72</v>
+        <v>39601.75</v>
       </c>
       <c r="F54" t="n">
-        <v>6843.77</v>
+        <v>24945.66</v>
       </c>
       <c r="G54" t="n">
-        <v>34727.95</v>
+        <v>14656.09</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>9882</t>
+          <t>8903</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>固定资产1</t>
+          <t>管理费用12</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>固定资产</t>
+          <t>管理费用</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>资产</t>
+          <t>成本</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>14107.61</v>
+        <v>44437.75</v>
       </c>
       <c r="F55" t="n">
-        <v>1017.38</v>
+        <v>36270.32</v>
       </c>
       <c r="G55" t="n">
-        <v>13090.23</v>
+        <v>8167.43</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6752</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>主营业务收入3</t>
+          <t>应付账款6</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>主营业务收入</t>
+          <t>应付账款</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>损益</t>
+          <t>负债</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>41193.41</v>
+        <v>35945.19</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>30613.89</v>
       </c>
       <c r="G56" t="n">
-        <v>41193.41</v>
+        <v>5331.300000000003</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>4478</t>
+          <t>2318</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>应付账款1</t>
+          <t>短期借款11</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>应付账款</t>
+          <t>短期借款</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2144,91 +2159,91 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2116.22</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>19201.6</v>
+        <v>33530.08</v>
       </c>
       <c r="G57" t="n">
-        <v>-17085.38</v>
+        <v>-33530.08</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>8777</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>应收账款1</t>
+          <t>长期借款9</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>应收账款</t>
+          <t>长期借款</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>资产</t>
+          <t>负债</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>30549.6</v>
+        <v>6863.26</v>
       </c>
       <c r="F58" t="n">
-        <v>29522.58</v>
+        <v>45193.91</v>
       </c>
       <c r="G58" t="n">
-        <v>1027.019999999997</v>
+        <v>-38330.65</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>5746</t>
+          <t>7823</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>长期借款7</t>
+          <t>盈余公积6</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>长期借款</t>
+          <t>盈余公积</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>负债</t>
+          <t>权益</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>11598.58</v>
+        <v>28367.78</v>
       </c>
       <c r="F59" t="n">
-        <v>29712.44</v>
+        <v>40370.68</v>
       </c>
       <c r="G59" t="n">
-        <v>-18113.86</v>
+        <v>-12002.9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>5790</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>现金10</t>
+          <t>银行存款13</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>现金</t>
+          <t>银行存款</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2237,415 +2252,427 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>19200.43</v>
+        <v>24485.94</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>15637.5</v>
       </c>
       <c r="G60" t="n">
-        <v>19200.43</v>
+        <v>8848.439999999999</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>盈余公积8</t>
+          <t>固定资产9</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>盈余公积</t>
+          <t>固定资产</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>权益</t>
+          <t>资产</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4660.79</v>
+        <v>40317.67</v>
       </c>
       <c r="F61" t="n">
-        <v>10088.58</v>
+        <v>1192.94</v>
       </c>
       <c r="G61" t="n">
-        <v>-5427.79</v>
+        <v>39124.73</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>9560</t>
+          <t>1583</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>盈余公积12</t>
+          <t>应付账款4</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>盈余公积</t>
+          <t>应付账款</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>权益</t>
+          <t>负债</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>41953.65</v>
+        <v>29079.34</v>
       </c>
       <c r="F62" t="n">
-        <v>16332.46</v>
+        <v>43592.05</v>
       </c>
       <c r="G62" t="n">
-        <v>25621.19</v>
+        <v>-14512.71</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>应付账款7</t>
+          <t>管理费用1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>应付账款</t>
+          <t>管理费用</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>负债</t>
-        </is>
+          <t>成本</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>7001.29</v>
       </c>
       <c r="F63" t="n">
-        <v>47236.54</v>
+        <v>33446.15</v>
       </c>
       <c r="G63" t="n">
-        <v>-10000.81</v>
+        <v>-26444.86</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2979</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>存货1</t>
+          <t>短期借款5</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>存货</t>
+          <t>短期借款</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>资产</t>
+          <t>负债</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>42224.45</v>
+        <v>16510.44</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>11904.39</v>
       </c>
       <c r="G64" t="n">
-        <v>42224.45</v>
+        <v>4606.049999999999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3970</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>存货3</t>
+          <t>管理费用11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>存货</t>
+          <t>管理费用</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>资产</t>
-        </is>
+          <t>成本</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>22165.74</v>
       </c>
       <c r="F65" t="n">
-        <v>31723.98</v>
+        <v>35288.68</v>
       </c>
       <c r="G65" t="n">
-        <v>-30465.99</v>
+        <v>-13122.94</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>9696</t>
+          <t>8948</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>现金2</t>
+          <t>主营业务收入2</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>现金</t>
+          <t>主营业务收入</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>资产</t>
+          <t>损益</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>41578.36</v>
       </c>
       <c r="F66" t="n">
-        <v>24841.69</v>
+        <v>27375.74</v>
       </c>
       <c r="G66" t="n">
-        <v>-24841.69</v>
+        <v>14202.62</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3928</t>
+          <t>5964</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>存货13</t>
+          <t>投资收益6</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>存货</t>
+          <t>投资收益</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>资产</t>
-        </is>
+          <t>损益</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>20044.01</v>
+        <v>1599.1</v>
       </c>
       <c r="G67" t="n">
-        <v>29516.49</v>
+        <v>-1599.1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>3454</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>短期借款9</t>
+          <t>主营业务成本13</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>短期借款</t>
+          <t>主营业务成本</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>负债</t>
+          <t>成本</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>42772.41</v>
+        <v>30947.22</v>
       </c>
       <c r="F68" t="n">
-        <v>19109</v>
+        <v>37584.06</v>
       </c>
       <c r="G68" t="n">
-        <v>23663.41</v>
+        <v>-6636.839999999997</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4464</t>
+          <t>8776</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>投资收益8</t>
+          <t>存货4</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>投资收益</t>
+          <t>存货</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>损益</t>
+          <t>资产</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4686.66</v>
+        <v>5731.02</v>
       </c>
       <c r="F69" t="n">
-        <v>42876.08</v>
+        <v>26858.22</v>
       </c>
       <c r="G69" t="n">
-        <v>-38189.42</v>
+        <v>-21127.2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1753</t>
+          <t>3487</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>应付账款15</t>
+          <t>主营业务收入10</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>应付账款</t>
+          <t>主营业务收入</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>负债</t>
+          <t>损益</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>29532.65</v>
+        <v>34505.55</v>
       </c>
       <c r="F70" t="n">
-        <v>31059.74</v>
+        <v>36791.24</v>
       </c>
       <c r="G70" t="n">
-        <v>-1527.09</v>
+        <v>-2285.689999999995</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>8048</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>盈余公积11</t>
+          <t>管理费用8</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>盈余公积</t>
+          <t>管理费用</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>权益</t>
-        </is>
+          <t>成本</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>24551.83</v>
       </c>
       <c r="F71" t="n">
-        <v>39686.28</v>
+        <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>-34376.79</v>
+        <v>24551.83</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>8766</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>现金9</t>
+          <t>实收资本3</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>现金</t>
+          <t>实收资本</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>资产</t>
+          <t>权益</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>31801.53</v>
+        <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>17559.76</v>
+        <v>31947.83</v>
       </c>
       <c r="G72" t="n">
-        <v>14241.77</v>
+        <v>-31947.83</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>6253</t>
+          <t>9288</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>管理费用13</t>
+          <t>应付账款10</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>管理费用</t>
+          <t>应付账款</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>成本</t>
+          <t>负债</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>48350.8</v>
+        <v>1657.46</v>
       </c>
       <c r="F73" t="n">
-        <v>49343.91</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>-993.1100000000006</v>
+        <v>1657.46</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>应付账款10</t>
+          <t>应付账款1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2659,57 +2686,60 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>25801.5</v>
+        <v>45233.19</v>
       </c>
       <c r="F74" t="n">
-        <v>48646.14</v>
+        <v>15939.63</v>
       </c>
       <c r="G74" t="n">
-        <v>-22844.64</v>
+        <v>29293.56</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>9878</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>应收账款10</t>
+          <t>投资收益12</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>应收账款</t>
+          <t>投资收益</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>资产</t>
-        </is>
+          <t>损益</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>1406.43</v>
       </c>
       <c r="F75" t="n">
-        <v>8438.9</v>
+        <v>43344.17</v>
       </c>
       <c r="G75" t="n">
-        <v>14466.4</v>
+        <v>-41937.74</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5157</t>
+          <t>3898</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>银行存款6</t>
+          <t>存货2</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>银行存款</t>
+          <t>存货</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2718,29 +2748,29 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>21159.13</v>
+        <v>41096.23</v>
       </c>
       <c r="F76" t="n">
-        <v>38197.32</v>
+        <v>10143.08</v>
       </c>
       <c r="G76" t="n">
-        <v>-17038.19</v>
+        <v>30953.15</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5379</t>
+          <t>3014</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>固定资产10</t>
+          <t>应收账款8</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>固定资产</t>
+          <t>应收账款</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2749,60 +2779,60 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>26566.77</v>
+        <v>9995.26</v>
       </c>
       <c r="F77" t="n">
-        <v>27344.27</v>
+        <v>17211.88</v>
       </c>
       <c r="G77" t="n">
-        <v>-777.5</v>
+        <v>-7216.620000000001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>主营业务成本8</t>
+          <t>投资收益13</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>主营业务成本</t>
+          <t>投资收益</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>成本</t>
+          <t>损益</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>31407.05</v>
+        <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>5306.54</v>
+        <v>34626.31</v>
       </c>
       <c r="G78" t="n">
-        <v>26100.51</v>
+        <v>-34626.31</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4496</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>存货2</t>
+          <t>应收账款11</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>存货</t>
+          <t>应收账款</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2810,58 +2840,58 @@
           <t>资产</t>
         </is>
       </c>
-      <c r="E79" t="n">
-        <v>20631.51</v>
-      </c>
       <c r="F79" t="n">
-        <v>1294.42</v>
+        <v>38068.71</v>
       </c>
       <c r="G79" t="n">
-        <v>19337.09</v>
+        <v>-7853.239999999998</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>6293</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>盈余公积1</t>
+          <t>应付账款8</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>盈余公积</t>
+          <t>应付账款</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>权益</t>
-        </is>
+          <t>负债</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>11479.26</v>
+        <v>49797.43</v>
       </c>
       <c r="G80" t="n">
-        <v>17991.08</v>
+        <v>-49797.43</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>6177</t>
+          <t>4078</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>投资收益5</t>
+          <t>主营业务收入12</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>投资收益</t>
+          <t>主营业务收入</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2870,29 +2900,29 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>15612.01</v>
+        <v>27418.59</v>
       </c>
       <c r="F81" t="n">
-        <v>37744.96</v>
+        <v>49626.94</v>
       </c>
       <c r="G81" t="n">
-        <v>-22132.95</v>
+        <v>-22208.35</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>2762</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>管理费用3</t>
+          <t>主营业务成本5</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>管理费用</t>
+          <t>主营业务成本</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2901,29 +2931,29 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>37367.1</v>
+        <v>40010.67</v>
       </c>
       <c r="F82" t="n">
-        <v>27372.99</v>
+        <v>10777.1</v>
       </c>
       <c r="G82" t="n">
-        <v>9994.109999999997</v>
+        <v>29233.57</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5034</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>应收账款4</t>
+          <t>现金5</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>应收账款</t>
+          <t>现金</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2931,22 +2961,25 @@
           <t>资产</t>
         </is>
       </c>
+      <c r="E83" t="n">
+        <v>44064.95</v>
+      </c>
       <c r="F83" t="n">
-        <v>35786.49</v>
+        <v>35195.99</v>
       </c>
       <c r="G83" t="n">
-        <v>-35786.49</v>
+        <v>8868.959999999999</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>3287</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>现金3</t>
+          <t>现金6</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2960,184 +2993,184 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3910.67</v>
+        <v>33221.09</v>
       </c>
       <c r="F84" t="n">
-        <v>44740.06</v>
+        <v>21843.6</v>
       </c>
       <c r="G84" t="n">
-        <v>-40829.39</v>
+        <v>11377.49</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5831</t>
+          <t>8788</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>盈余公积13</t>
+          <t>主营业务成本12</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>盈余公积</t>
+          <t>主营业务成本</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>权益</t>
+          <t>成本</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1296.58</v>
+        <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>38967.74</v>
+        <v>6110.47</v>
       </c>
       <c r="G85" t="n">
-        <v>-37671.16</v>
+        <v>-6110.47</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>8135</t>
+          <t>4360</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>主营业务收入6</t>
+          <t>盈余公积7</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>主营业务收入</t>
+          <t>盈余公积</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>损益</t>
+          <t>权益</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>43037.24</v>
+        <v>8669.879999999999</v>
       </c>
       <c r="F86" t="n">
-        <v>41794.61</v>
+        <v>25299.25</v>
       </c>
       <c r="G86" t="n">
-        <v>1242.629999999997</v>
+        <v>-16629.37</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>6773</t>
+          <t>7711</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>主营业务收入13</t>
+          <t>管理费用6</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>主营业务收入</t>
+          <t>管理费用</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>损益</t>
+          <t>成本</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>49905.41</v>
+        <v>25637.05</v>
       </c>
       <c r="F87" t="n">
-        <v>17066.37</v>
+        <v>26487.61</v>
       </c>
       <c r="G87" t="n">
-        <v>32839.04000000001</v>
+        <v>-850.5600000000013</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>6073</t>
+          <t>8680</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>主营业务收入11</t>
+          <t>存货8</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>主营业务收入</t>
+          <t>存货</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>损益</t>
+          <t>资产</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>21389.88</v>
+        <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>23437.47</v>
+        <v>10585.88</v>
       </c>
       <c r="G88" t="n">
-        <v>-2047.59</v>
+        <v>-10585.88</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>5595</t>
+          <t>8592</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>主营业务收入2</t>
+          <t>银行存款4</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>主营业务收入</t>
+          <t>银行存款</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>损益</t>
+          <t>资产</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>31610.84</v>
+        <v>10845.19</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>41160.73</v>
       </c>
       <c r="G89" t="n">
-        <v>31610.84</v>
+        <v>-30315.54</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3164</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>固定资产2</t>
+          <t>银行存款12</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>固定资产</t>
+          <t>银行存款</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3145,272 +3178,278 @@
           <t>资产</t>
         </is>
       </c>
+      <c r="E90" t="n">
+        <v>44441.15</v>
+      </c>
       <c r="F90" t="n">
-        <v>45160.73</v>
+        <v>33760.73</v>
       </c>
       <c r="G90" t="n">
-        <v>-25190.66</v>
+        <v>10680.42</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>5595</t>
+          <t>2418</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>长期借款4</t>
+          <t>投资收益5</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>长期借款</t>
+          <t>投资收益</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>负债</t>
+          <t>损益</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5231.36</v>
+        <v>43789.89</v>
       </c>
       <c r="F91" t="n">
-        <v>41068.79</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>-35837.43</v>
+        <v>43789.89</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>7009</t>
+          <t>6428</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>银行存款10</t>
+          <t>实收资本9</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>银行存款</t>
+          <t>实收资本</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>资产</t>
+          <t>权益</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5705.76</v>
+        <v>26512.84</v>
       </c>
       <c r="F92" t="n">
-        <v>47298.28</v>
+        <v>43261.67</v>
       </c>
       <c r="G92" t="n">
-        <v>-41592.52</v>
+        <v>-16748.83</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>4278</t>
+          <t>6158</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>投资收益1</t>
+          <t>银行存款5</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>投资收益</t>
+          <t>银行存款</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>损益</t>
+          <t>资产</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>17827.4</v>
       </c>
       <c r="F93" t="n">
-        <v>12046.8</v>
+        <v>47403.24</v>
       </c>
       <c r="G93" t="n">
-        <v>-12046.8</v>
+        <v>-29575.84</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>9256</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>管理费用9</t>
+          <t>投资收益3</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>管理费用</t>
+          <t>投资收益</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>成本</t>
-        </is>
+          <t>损益</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>24020.61</v>
       </c>
       <c r="F94" t="n">
-        <v>38924.37</v>
+        <v>26842.96</v>
       </c>
       <c r="G94" t="n">
-        <v>-7018.630000000001</v>
+        <v>-2822.349999999999</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>6628</t>
+          <t>8914</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>应付账款14</t>
+          <t>现金8</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>应付账款</t>
+          <t>现金</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>负债</t>
+          <t>资产</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>33937.73</v>
+        <v>37830.31</v>
       </c>
       <c r="F95" t="n">
-        <v>36582.29</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>-2644.559999999998</v>
+        <v>37830.31</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>6878</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>短期借款12</t>
+          <t>实收资本12</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>短期借款</t>
+          <t>实收资本</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>负债</t>
+          <t>权益</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>29684.4</v>
+        <v>1017.37</v>
       </c>
       <c r="F96" t="n">
-        <v>42372.65</v>
+        <v>45523.65</v>
       </c>
       <c r="G96" t="n">
-        <v>-12688.25</v>
+        <v>-44506.28</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>9243</t>
+          <t>4907</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>应收账款3</t>
+          <t>主营业务收入5</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>应收账款</t>
+          <t>主营业务收入</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>资产</t>
+          <t>损益</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>32775.26</v>
+        <v>34456</v>
       </c>
       <c r="F97" t="n">
-        <v>40707.49</v>
+        <v>48059.29</v>
       </c>
       <c r="G97" t="n">
-        <v>-7932.229999999996</v>
+        <v>-13603.29</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2393</t>
+          <t>6570</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>主营业务成本10</t>
+          <t>长期借款6</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>主营业务成本</t>
+          <t>长期借款</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>成本</t>
+          <t>负债</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>41521.99</v>
+        <v>39694.56</v>
       </c>
       <c r="F98" t="n">
-        <v>23059.89</v>
+        <v>25688.54</v>
       </c>
       <c r="G98" t="n">
-        <v>18462.1</v>
+        <v>14006.02</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>7331</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>存货11</t>
+          <t>固定资产6</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>存货</t>
+          <t>固定资产</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3419,184 +3458,181 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>26724.22</v>
+        <v>47574.06</v>
       </c>
       <c r="F99" t="n">
-        <v>33418.82</v>
+        <v>14767.39</v>
       </c>
       <c r="G99" t="n">
-        <v>-6694.599999999999</v>
+        <v>32806.67</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>6615</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>主营业务成本13</t>
+          <t>固定资产3</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>主营业务成本</t>
+          <t>固定资产</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>成本</t>
+          <t>资产</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>41034.58</v>
+        <v>45960.82</v>
       </c>
       <c r="F100" t="n">
-        <v>40062.18</v>
+        <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>972.4000000000015</v>
+        <v>45960.82</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>3690</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>盈余公积4</t>
+          <t>现金11</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>盈余公积</t>
+          <t>现金</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>权益</t>
-        </is>
-      </c>
-      <c r="E101" t="n">
-        <v>29826.67</v>
+          <t>资产</t>
+        </is>
       </c>
       <c r="F101" t="n">
-        <v>36253.47</v>
+        <v>30188.26</v>
       </c>
       <c r="G101" t="n">
-        <v>-6426.800000000003</v>
+        <v>-24904.26</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>9340</t>
+          <t>6561</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>实收资本9</t>
+          <t>应收账款4</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>实收资本</t>
+          <t>应收账款</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>权益</t>
+          <t>资产</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>3389.76</v>
+        <v>30872.52</v>
       </c>
       <c r="F102" t="n">
-        <v>6393.08</v>
+        <v>22034.98</v>
       </c>
       <c r="G102" t="n">
-        <v>-3003.32</v>
+        <v>8837.540000000001</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>6049</t>
+          <t>5254</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>应收账款2</t>
+          <t>短期借款10</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>应收账款</t>
+          <t>短期借款</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>资产</t>
+          <t>负债</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>40482.01</v>
+        <v>36746.2</v>
       </c>
       <c r="F103" t="n">
-        <v>12683.63</v>
+        <v>21661.16</v>
       </c>
       <c r="G103" t="n">
-        <v>27798.38</v>
+        <v>15085.04</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2547</t>
+          <t>4755</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>长期借款11</t>
+          <t>盈余公积5</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>长期借款</t>
+          <t>盈余公积</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>负债</t>
+          <t>权益</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>20073.91</v>
+        <v>28252.55</v>
       </c>
       <c r="F104" t="n">
-        <v>1895.43</v>
+        <v>28492.36</v>
       </c>
       <c r="G104" t="n">
-        <v>18178.48</v>
+        <v>-239.8100000000013</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>4413</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>长期借款9</t>
+          <t>短期借款7</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>长期借款</t>
+          <t>短期借款</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3605,86 +3641,86 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>41238.07</v>
+        <v>49343.18</v>
       </c>
       <c r="F105" t="n">
-        <v>40397.88</v>
+        <v>10277.49</v>
       </c>
       <c r="G105" t="n">
-        <v>840.1900000000023</v>
+        <v>39065.69</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>8250</t>
+          <t>8459</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>管理费用12</t>
+          <t>应收账款9</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>管理费用</t>
+          <t>应收账款</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>成本</t>
+          <t>资产</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2242.34</v>
+        <v>21764.42</v>
       </c>
       <c r="F106" t="n">
-        <v>45553.48</v>
+        <v>13201.84</v>
       </c>
       <c r="G106" t="n">
-        <v>-43311.14</v>
+        <v>8562.579999999998</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>应付账款8</t>
+          <t>主营业务成本3</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>应付账款</t>
+          <t>主营业务成本</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>负债</t>
+          <t>成本</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5299.99</v>
+        <v>3501.59</v>
       </c>
       <c r="F107" t="n">
-        <v>8240.540000000001</v>
+        <v>12161.12</v>
       </c>
       <c r="G107" t="n">
-        <v>-2940.550000000001</v>
+        <v>-8659.530000000001</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>9820</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>现金5</t>
+          <t>现金7</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3698,271 +3734,274 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>24693.08</v>
+        <v>14344.35</v>
       </c>
       <c r="F108" t="n">
-        <v>7413.95</v>
+        <v>14426.74</v>
       </c>
       <c r="G108" t="n">
-        <v>17279.13</v>
+        <v>-82.38999999999942</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>6215</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>短期借款11</t>
+          <t>银行存款7</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>短期借款</t>
+          <t>银行存款</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>负债</t>
-        </is>
+          <t>资产</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>34012.33</v>
       </c>
       <c r="F109" t="n">
-        <v>39381.81</v>
+        <v>35048.99</v>
       </c>
       <c r="G109" t="n">
-        <v>-21749.36</v>
+        <v>-1036.659999999996</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>9211</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>现金7</t>
+          <t>实收资本2</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>现金</t>
+          <t>实收资本</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>资产</t>
+          <t>权益</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>17102.5</v>
+        <v>45373.51</v>
       </c>
       <c r="F110" t="n">
-        <v>43867.72</v>
+        <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>-26765.22</v>
+        <v>45373.51</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>6137</t>
+          <t>7209</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>短期借款4</t>
+          <t>管理费用5</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>短期借款</t>
+          <t>管理费用</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>负债</t>
-        </is>
-      </c>
-      <c r="E111" t="n">
-        <v>8866.91</v>
+          <t>成本</t>
+        </is>
       </c>
       <c r="F111" t="n">
-        <v>32369.19</v>
+        <v>14787.28</v>
       </c>
       <c r="G111" t="n">
-        <v>-23502.28</v>
+        <v>-7923.870000000001</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2522</t>
+          <t>8648</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>管理费用1</t>
+          <t>投资收益10</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>管理费用</t>
+          <t>投资收益</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>成本</t>
+          <t>损益</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>22672.47</v>
+        <v>4678.11</v>
       </c>
       <c r="F112" t="n">
-        <v>23410.9</v>
+        <v>29063.5</v>
       </c>
       <c r="G112" t="n">
-        <v>-738.4300000000003</v>
+        <v>-24385.39</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>9619</t>
+          <t>7313</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>主营业务成本2</t>
+          <t>应收账款10</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>主营业务成本</t>
+          <t>应收账款</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>成本</t>
-        </is>
+          <t>资产</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>46360.77</v>
       </c>
       <c r="F113" t="n">
-        <v>19280.29</v>
+        <v>30561.12</v>
       </c>
       <c r="G113" t="n">
-        <v>27967.45</v>
+        <v>15799.65</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>9305</t>
+          <t>4223</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>盈余公积6</t>
+          <t>短期借款3</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>盈余公积</t>
+          <t>短期借款</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>权益</t>
+          <t>负债</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>28574.5</v>
+        <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>38249.66</v>
+        <v>43713.66</v>
       </c>
       <c r="G114" t="n">
-        <v>-9675.160000000003</v>
+        <v>-43713.66</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1603</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>固定资产3</t>
+          <t>主营业务成本11</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>固定资产</t>
+          <t>主营业务成本</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>资产</t>
+          <t>成本</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>9600.370000000001</v>
+        <v>31078.62</v>
       </c>
       <c r="F115" t="n">
-        <v>0</v>
+        <v>1984.28</v>
       </c>
       <c r="G115" t="n">
-        <v>9600.370000000001</v>
+        <v>29094.34</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>6380</t>
+          <t>2649</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>盈余公积3</t>
+          <t>应收账款12</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>盈余公积</t>
+          <t>应收账款</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>权益</t>
+          <t>资产</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>27275.55</v>
+        <v>15135.69</v>
       </c>
       <c r="F116" t="n">
-        <v>28128.87</v>
+        <v>43088.46</v>
       </c>
       <c r="G116" t="n">
-        <v>-853.3199999999997</v>
+        <v>-27952.77</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>3913</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>现金8</t>
+          <t>银行存款9</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>现金</t>
+          <t>银行存款</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3971,52 +4010,55 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0</v>
+        <v>44378.8</v>
       </c>
       <c r="F117" t="n">
-        <v>26125.68</v>
+        <v>13933.82</v>
       </c>
       <c r="G117" t="n">
-        <v>-26125.68</v>
+        <v>30444.98</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>短期借款7</t>
+          <t>管理费用10</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>短期借款</t>
+          <t>管理费用</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>负债</t>
-        </is>
+          <t>成本</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>12064.9</v>
       </c>
       <c r="F118" t="n">
-        <v>1343.31</v>
+        <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>28299.2</v>
+        <v>12064.9</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>4277</t>
+          <t>6181</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>短期借款6</t>
+          <t>短期借款8</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4029,61 +4071,58 @@
           <t>负债</t>
         </is>
       </c>
-      <c r="E119" t="n">
-        <v>9545.190000000001</v>
-      </c>
       <c r="F119" t="n">
-        <v>21319.19</v>
+        <v>30432.57</v>
       </c>
       <c r="G119" t="n">
-        <v>-11774</v>
+        <v>-12336.17</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>7211</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>短期借款8</t>
+          <t>应收账款5</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>短期借款</t>
+          <t>应收账款</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>负债</t>
+          <t>资产</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>33942</v>
+        <v>14456</v>
       </c>
       <c r="F120" t="n">
-        <v>31629.8</v>
+        <v>33652.69</v>
       </c>
       <c r="G120" t="n">
-        <v>2312.200000000001</v>
+        <v>-19196.69</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>7175</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>主营业务成本7</t>
+          <t>管理费用13</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>主营业务成本</t>
+          <t>管理费用</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4092,24 +4131,24 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>46876.03</v>
+        <v>10363.53</v>
       </c>
       <c r="F121" t="n">
-        <v>2771.72</v>
+        <v>3449</v>
       </c>
       <c r="G121" t="n">
-        <v>44104.31</v>
+        <v>6914.530000000001</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>3722</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>银行存款11</t>
+          <t>银行存款3</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4123,424 +4162,421 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>7874.23</v>
+        <v>39848.81</v>
       </c>
       <c r="F122" t="n">
-        <v>33871.88</v>
+        <v>33320.57</v>
       </c>
       <c r="G122" t="n">
-        <v>-25997.65</v>
+        <v>6528.239999999998</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>8183</t>
+          <t>9710</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>主营业务成本11</t>
+          <t>投资收益9</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>主营业务成本</t>
+          <t>投资收益</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>成本</t>
+          <t>损益</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>11532.89</v>
+        <v>40420.73</v>
       </c>
       <c r="F123" t="n">
-        <v>26122.99</v>
+        <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>-14590.1</v>
+        <v>40420.73</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>管理费用7</t>
+          <t>实收资本6</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>管理费用</t>
+          <t>实收资本</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>成本</t>
+          <t>权益</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>13147.6</v>
+        <v>15654.09</v>
       </c>
       <c r="G124" t="n">
-        <v>12128.84</v>
+        <v>13520.12</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>3484</t>
+          <t>3498</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>应收账款8</t>
+          <t>管理费用2</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>应收账款</t>
+          <t>管理费用</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>资产</t>
+          <t>成本</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>36743.44</v>
+        <v>1401.71</v>
       </c>
       <c r="F125" t="n">
-        <v>31418.65</v>
+        <v>37028.8</v>
       </c>
       <c r="G125" t="n">
-        <v>5324.790000000001</v>
+        <v>-35627.09</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>5275</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>投资收益11</t>
+          <t>现金1</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>投资收益</t>
+          <t>现金</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>损益</t>
+          <t>资产</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0</v>
+        <v>44280.3</v>
       </c>
       <c r="F126" t="n">
-        <v>47935.86</v>
+        <v>14161.44</v>
       </c>
       <c r="G126" t="n">
-        <v>-47935.86</v>
+        <v>30118.86</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>5877</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>存货10</t>
+          <t>主营业务成本7</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>存货</t>
+          <t>主营业务成本</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>资产</t>
+          <t>成本</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>46152.17</v>
+        <v>40865.29</v>
       </c>
       <c r="F127" t="n">
-        <v>46114.28</v>
+        <v>36469.63</v>
       </c>
       <c r="G127" t="n">
-        <v>37.88999999999942</v>
+        <v>4395.660000000003</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>8843</t>
+          <t>3421</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>实收资本10</t>
+          <t>应收账款3</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>实收资本</t>
+          <t>应收账款</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>权益</t>
+          <t>资产</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>45141.22</v>
+        <v>31961.4</v>
       </c>
       <c r="F128" t="n">
-        <v>45089.53</v>
+        <v>15976.17</v>
       </c>
       <c r="G128" t="n">
-        <v>51.69000000000233</v>
+        <v>15985.23</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>9128</t>
+          <t>7433</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>应收账款6</t>
+          <t>长期借款7</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>应收账款</t>
+          <t>长期借款</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>资产</t>
+          <t>负债</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>49547.11</v>
+        <v>24704.69</v>
       </c>
       <c r="F129" t="n">
-        <v>42613.97</v>
+        <v>13151.55</v>
       </c>
       <c r="G129" t="n">
-        <v>6933.139999999999</v>
+        <v>11553.14</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>长期借款12</t>
+          <t>应收账款7</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>长期借款</t>
+          <t>应收账款</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>负债</t>
+          <t>资产</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>38809.78</v>
+        <v>42900.26</v>
       </c>
       <c r="F130" t="n">
-        <v>20873.79</v>
+        <v>5099.47</v>
       </c>
       <c r="G130" t="n">
-        <v>17935.99</v>
+        <v>37800.79</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>投资收益4</t>
+          <t>盈余公积1</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>投资收益</t>
+          <t>盈余公积</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>损益</t>
+          <t>权益</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1986.4</v>
+        <v>28989.07</v>
       </c>
       <c r="F131" t="n">
-        <v>48339.68</v>
+        <v>13672.13</v>
       </c>
       <c r="G131" t="n">
-        <v>-46353.28</v>
+        <v>15316.94</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>4292</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>实收资本5</t>
+          <t>短期借款1</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>实收资本</t>
+          <t>短期借款</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>权益</t>
-        </is>
-      </c>
-      <c r="E132" t="n">
-        <v>35591.83</v>
+          <t>负债</t>
+        </is>
       </c>
       <c r="F132" t="n">
-        <v>2469.97</v>
+        <v>47468.96</v>
       </c>
       <c r="G132" t="n">
-        <v>33121.86</v>
+        <v>-29111.43</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>3941</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>管理费用4</t>
+          <t>短期借款2</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>管理费用</t>
+          <t>短期借款</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>成本</t>
+          <t>负债</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>32773.08</v>
+        <v>20351.64</v>
       </c>
       <c r="F133" t="n">
-        <v>42289.88</v>
+        <v>27113.96</v>
       </c>
       <c r="G133" t="n">
-        <v>-9516.799999999996</v>
+        <v>-6762.32</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2463</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>投资收益2</t>
+          <t>应收账款15</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>投资收益</t>
+          <t>应收账款</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>损益</t>
+          <t>资产</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>9221.440000000001</v>
+        <v>6100.93</v>
       </c>
       <c r="F134" t="n">
-        <v>32899.38</v>
+        <v>33272.86</v>
       </c>
       <c r="G134" t="n">
-        <v>-23677.94</v>
+        <v>-27171.93</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>6338</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>应付账款11</t>
+          <t>应收账款6</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>应付账款</t>
+          <t>应收账款</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>负债</t>
+          <t>资产</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>16901.64</v>
+        <v>10915.68</v>
       </c>
       <c r="F135" t="n">
-        <v>7344.56</v>
+        <v>11728.66</v>
       </c>
       <c r="G135" t="n">
-        <v>9557.079999999998</v>
+        <v>-812.9799999999996</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>8423</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>主营业务收入4</t>
+          <t>主营业务收入11</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4554,384 +4590,387 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2533.27</v>
+        <v>19746.12</v>
       </c>
       <c r="F136" t="n">
-        <v>44569.32</v>
+        <v>22682.77</v>
       </c>
       <c r="G136" t="n">
-        <v>-42036.05</v>
+        <v>-2936.650000000001</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>5890</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>存货9</t>
+          <t>实收资本7</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>存货</t>
+          <t>实收资本</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>资产</t>
+          <t>权益</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6313.24</v>
+        <v>17332.49</v>
       </c>
       <c r="F137" t="n">
-        <v>16602.37</v>
+        <v>2564.14</v>
       </c>
       <c r="G137" t="n">
-        <v>-10289.13</v>
+        <v>14768.35</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>4842</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>银行存款9</t>
+          <t>主营业务收入14</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>银行存款</t>
+          <t>主营业务收入</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>资产</t>
+          <t>损益</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>29340.12</v>
+        <v>14852.63</v>
       </c>
       <c r="G138" t="n">
-        <v>-6015.299999999999</v>
+        <v>-6446.209999999999</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>9928</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>主营业务成本5</t>
+          <t>固定资产4</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>主营业务成本</t>
+          <t>固定资产</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>成本</t>
+          <t>资产</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>35163.27</v>
+        <v>34396.96</v>
       </c>
       <c r="F139" t="n">
-        <v>34924</v>
+        <v>48314.1</v>
       </c>
       <c r="G139" t="n">
-        <v>239.2699999999968</v>
+        <v>-13917.14</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>存货12</t>
+          <t>长期借款3</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>存货</t>
+          <t>长期借款</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>资产</t>
+          <t>负债</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1266.45</v>
+        <v>37764.45</v>
       </c>
       <c r="F140" t="n">
-        <v>1604.92</v>
+        <v>25847.64</v>
       </c>
       <c r="G140" t="n">
-        <v>-338.47</v>
+        <v>11916.81</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>4236</t>
+          <t>6253</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>银行存款5</t>
+          <t>主营业务收入1</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>银行存款</t>
+          <t>主营业务收入</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>资产</t>
+          <t>损益</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>41285.73</v>
+        <v>40284.72</v>
       </c>
       <c r="G141" t="n">
-        <v>-7772.150000000001</v>
+        <v>-1052.349999999999</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>3118</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>主营业务成本12</t>
+          <t>固定资产7</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>主营业务成本</t>
+          <t>固定资产</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>成本</t>
+          <t>资产</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>9210.790000000001</v>
+        <v>26916.1</v>
       </c>
       <c r="F142" t="n">
-        <v>13649.91</v>
+        <v>43526.53</v>
       </c>
       <c r="G142" t="n">
-        <v>-4439.119999999999</v>
+        <v>-16610.43</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>实收资本6</t>
+          <t>存货7</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>实收资本</t>
+          <t>存货</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>权益</t>
-        </is>
+          <t>资产</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>48692.87</v>
       </c>
       <c r="F143" t="n">
-        <v>41799.54</v>
+        <v>23316.74</v>
       </c>
       <c r="G143" t="n">
-        <v>-10022.75</v>
+        <v>25376.13</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>应收账款9</t>
+          <t>应付账款2</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>应收账款</t>
+          <t>应付账款</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>资产</t>
-        </is>
+          <t>负债</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>28281.94</v>
       </c>
       <c r="F144" t="n">
-        <v>17975.49</v>
+        <v>10764</v>
       </c>
       <c r="G144" t="n">
-        <v>-8598.310000000001</v>
+        <v>17517.94</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>盈余公积7</t>
+          <t>主营业务成本9</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>盈余公积</t>
+          <t>主营业务成本</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>权益</t>
-        </is>
-      </c>
-      <c r="E145" t="n">
-        <v>47990.87</v>
+          <t>成本</t>
+        </is>
       </c>
       <c r="F145" t="n">
-        <v>3005.82</v>
+        <v>42607.35</v>
       </c>
       <c r="G145" t="n">
-        <v>44985.05</v>
+        <v>-6197.93</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>7552</t>
+          <t>8595</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>银行存款4</t>
+          <t>盈余公积3</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>银行存款</t>
+          <t>盈余公积</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>资产</t>
+          <t>权益</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>20289.8</v>
+        <v>8637.73</v>
       </c>
       <c r="F146" t="n">
-        <v>21632.49</v>
+        <v>44999.88</v>
       </c>
       <c r="G146" t="n">
-        <v>-1342.690000000002</v>
+        <v>-36362.14999999999</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>4128</t>
+          <t>9415</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>主营业务收入10</t>
+          <t>现金10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>主营业务收入</t>
+          <t>现金</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>损益</t>
+          <t>资产</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>10371.28</v>
+        <v>5054.36</v>
       </c>
       <c r="F147" t="n">
-        <v>40060.61</v>
+        <v>46144.42</v>
       </c>
       <c r="G147" t="n">
-        <v>-29689.33</v>
+        <v>-41090.06</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>7194</t>
+          <t>5780</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>应付账款2</t>
+          <t>投资收益7</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>应付账款</t>
+          <t>投资收益</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>负债</t>
+          <t>损益</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>14398.78</v>
+        <v>31430.74</v>
       </c>
       <c r="F148" t="n">
-        <v>3855.37</v>
+        <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>10543.41</v>
+        <v>31430.74</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>银行存款1</t>
+          <t>银行存款8</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4945,29 +4984,29 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>33110.41</v>
+        <v>14867.48</v>
       </c>
       <c r="F149" t="n">
-        <v>2556.73</v>
+        <v>33786.22</v>
       </c>
       <c r="G149" t="n">
-        <v>30553.68</v>
+        <v>-18918.74</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>5986</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>银行存款13</t>
+          <t>存货11</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>银行存款</t>
+          <t>存货</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -4976,91 +5015,91 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>32766.91</v>
+        <v>37097.53</v>
       </c>
       <c r="F150" t="n">
-        <v>7917.18</v>
+        <v>13419.8</v>
       </c>
       <c r="G150" t="n">
-        <v>24849.73</v>
+        <v>23677.73</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1581</t>
+          <t>5539</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>应付账款3</t>
+          <t>主营业务成本6</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>应付账款</t>
+          <t>主营业务成本</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>负债</t>
+          <t>成本</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>36271.07</v>
+        <v>46473.71</v>
       </c>
       <c r="F151" t="n">
-        <v>42978.05</v>
+        <v>6387.21</v>
       </c>
       <c r="G151" t="n">
-        <v>-6706.980000000003</v>
+        <v>40086.5</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>9377</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>现金11</t>
+          <t>长期借款4</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>现金</t>
+          <t>长期借款</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>资产</t>
+          <t>负债</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>30165.6</v>
+        <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>25603.71</v>
+        <v>40586.42</v>
       </c>
       <c r="G152" t="n">
-        <v>4561.889999999999</v>
+        <v>-40586.42</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>7736</t>
+          <t>1743</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>存货5</t>
+          <t>现金4</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>存货</t>
+          <t>现金</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -5069,24 +5108,24 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>8943.74</v>
+        <v>40025.18</v>
       </c>
       <c r="F153" t="n">
-        <v>5946.87</v>
+        <v>23490.73</v>
       </c>
       <c r="G153" t="n">
-        <v>2996.87</v>
+        <v>16534.45</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>5609</t>
+          <t>6281</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>实收资本3</t>
+          <t>实收资本5</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5100,29 +5139,29 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>48552.01</v>
+        <v>22779.93</v>
       </c>
       <c r="F154" t="n">
-        <v>11380.17</v>
+        <v>17862.8</v>
       </c>
       <c r="G154" t="n">
-        <v>37171.84</v>
+        <v>4917.130000000001</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>3080</t>
+          <t>3396</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>短期借款3</t>
+          <t>长期借款8</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>短期借款</t>
+          <t>长期借款</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -5131,29 +5170,29 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>13624.45</v>
+        <v>18794.44</v>
       </c>
       <c r="F155" t="n">
-        <v>0</v>
+        <v>49731.17</v>
       </c>
       <c r="G155" t="n">
-        <v>13624.45</v>
+        <v>-30936.73</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>3382</t>
+          <t>2254</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>应收账款5</t>
+          <t>存货10</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>应收账款</t>
+          <t>存货</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -5162,24 +5201,24 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1261.16</v>
+        <v>44941.26</v>
       </c>
       <c r="F156" t="n">
-        <v>15489.11</v>
+        <v>21522.42</v>
       </c>
       <c r="G156" t="n">
-        <v>-14227.95</v>
+        <v>23418.84</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>2574</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>长期借款2</t>
+          <t>长期借款12</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5193,55 +5232,52 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>37575.36</v>
+        <v>49166.33</v>
       </c>
       <c r="F157" t="n">
-        <v>24911.05</v>
+        <v>26024.43</v>
       </c>
       <c r="G157" t="n">
-        <v>12664.31</v>
+        <v>23141.9</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>5672</t>
+          <t>2918</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>盈余公积9</t>
+          <t>应收账款13</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>盈余公积</t>
+          <t>应收账款</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>权益</t>
-        </is>
-      </c>
-      <c r="E158" t="n">
-        <v>5806.77</v>
+          <t>资产</t>
+        </is>
       </c>
       <c r="F158" t="n">
-        <v>0</v>
+        <v>5561.73</v>
       </c>
       <c r="G158" t="n">
-        <v>5806.77</v>
+        <v>675.4300000000003</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>9154</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>存货8</t>
+          <t>存货1</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5255,179 +5291,176 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>18852.21</v>
+        <v>4678.27</v>
       </c>
       <c r="F159" t="n">
-        <v>37263.71</v>
+        <v>38039.77</v>
       </c>
       <c r="G159" t="n">
-        <v>-18411.5</v>
+        <v>-33361.5</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>6334</t>
+          <t>7915</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>固定资产12</t>
+          <t>短期借款9</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>固定资产</t>
+          <t>短期借款</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>资产</t>
+          <t>负债</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>39599.49</v>
+        <v>48497.99</v>
       </c>
       <c r="F160" t="n">
-        <v>24766.12</v>
+        <v>47045.13</v>
       </c>
       <c r="G160" t="n">
-        <v>14833.37</v>
+        <v>1452.860000000001</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2419</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>管理费用5</t>
+          <t>投资收益1</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>管理费用</t>
+          <t>投资收益</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>成本</t>
+          <t>损益</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>8096.14</v>
+        <v>5517.32</v>
       </c>
       <c r="F161" t="n">
-        <v>45234.26</v>
+        <v>18888.57</v>
       </c>
       <c r="G161" t="n">
-        <v>-37138.12</v>
+        <v>-13371.25</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>6170</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>投资收益3</t>
+          <t>长期借款2</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>投资收益</t>
+          <t>长期借款</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>损益</t>
+          <t>负债</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>23540.12</v>
+        <v>37045.82</v>
       </c>
       <c r="F162" t="n">
-        <v>3475.93</v>
+        <v>28695.18</v>
       </c>
       <c r="G162" t="n">
-        <v>20064.19</v>
+        <v>8350.639999999999</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>7422</t>
+          <t>6634</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>实收资本7</t>
+          <t>银行存款6</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>实收资本</t>
+          <t>银行存款</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>权益</t>
-        </is>
-      </c>
-      <c r="E163" t="n">
-        <v>16887.29</v>
+          <t>资产</t>
+        </is>
       </c>
       <c r="F163" t="n">
-        <v>37842.38</v>
+        <v>3825.51</v>
       </c>
       <c r="G163" t="n">
-        <v>-20955.09</v>
+        <v>44691.93</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>9940</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>固定资产4</t>
+          <t>主营业务收入8</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>固定资产</t>
+          <t>主营业务收入</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>资产</t>
+          <t>损益</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>0</v>
+        <v>46392.17</v>
       </c>
       <c r="F164" t="n">
-        <v>0</v>
+        <v>10537.42</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>35854.75</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2574</t>
+          <t>9060</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>存货4</t>
+          <t>存货6</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5440,58 +5473,58 @@
           <t>资产</t>
         </is>
       </c>
-      <c r="E165" t="n">
-        <v>21688.63</v>
-      </c>
       <c r="F165" t="n">
-        <v>19685.95</v>
+        <v>33580.44</v>
       </c>
       <c r="G165" t="n">
-        <v>2002.68</v>
+        <v>-33580.44</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>5424</t>
+          <t>1386</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>存货6</t>
+          <t>盈余公积11</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>存货</t>
+          <t>盈余公积</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>资产</t>
-        </is>
+          <t>权益</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>29311.25</v>
       </c>
       <c r="F166" t="n">
-        <v>10296.94</v>
+        <v>39141.11</v>
       </c>
       <c r="G166" t="n">
-        <v>18269.19</v>
+        <v>-9829.860000000001</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>6071</t>
+          <t>5592</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>应收账款13</t>
+          <t>固定资产8</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>应收账款</t>
+          <t>固定资产</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -5500,215 +5533,209 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>45964.41</v>
+        <v>37482.18</v>
       </c>
       <c r="F167" t="n">
-        <v>38121.61</v>
+        <v>15404.14</v>
       </c>
       <c r="G167" t="n">
-        <v>7842.800000000003</v>
+        <v>22078.04</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>8953</t>
+          <t>3956</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>实收资本1</t>
+          <t>应付账款11</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>实收资本</t>
+          <t>应付账款</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>权益</t>
-        </is>
-      </c>
-      <c r="E168" t="n">
-        <v>13251.42</v>
+          <t>负债</t>
+        </is>
       </c>
       <c r="F168" t="n">
-        <v>3485.79</v>
+        <v>6601.57</v>
       </c>
       <c r="G168" t="n">
-        <v>9765.630000000001</v>
+        <v>7507.93</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>6355</t>
+          <t>6799</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>实收资本4</t>
+          <t>银行存款1</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>实收资本</t>
+          <t>银行存款</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>权益</t>
-        </is>
-      </c>
-      <c r="E169" t="n">
-        <v>16054.55</v>
+          <t>资产</t>
+        </is>
       </c>
       <c r="F169" t="n">
-        <v>0</v>
+        <v>12062.21</v>
       </c>
       <c r="G169" t="n">
-        <v>16054.55</v>
+        <v>28192.18</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>3684</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>长期借款5</t>
+          <t>主营业务成本8</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>长期借款</t>
+          <t>主营业务成本</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>负债</t>
+          <t>成本</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>3050.16</v>
+        <v>13184.41</v>
       </c>
       <c r="F170" t="n">
-        <v>40003.79</v>
+        <v>20776.17</v>
       </c>
       <c r="G170" t="n">
-        <v>-36953.63</v>
+        <v>-7591.759999999998</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>主营业务收入5</t>
+          <t>应付账款5</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>主营业务收入</t>
+          <t>应付账款</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>损益</t>
+          <t>负债</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>20864.59</v>
+        <v>11743.16</v>
       </c>
       <c r="F171" t="n">
-        <v>24340.74</v>
+        <v>29444.06</v>
       </c>
       <c r="G171" t="n">
-        <v>-3476.150000000001</v>
+        <v>-17700.9</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>8764</t>
+          <t>7532</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>长期借款3</t>
+          <t>银行存款11</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>长期借款</t>
+          <t>银行存款</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>负债</t>
+          <t>资产</t>
         </is>
       </c>
       <c r="E172" t="n">
+        <v>48329.05</v>
+      </c>
+      <c r="F172" t="n">
         <v>0</v>
       </c>
-      <c r="F172" t="n">
-        <v>30167.91</v>
-      </c>
       <c r="G172" t="n">
-        <v>-30167.91</v>
+        <v>48329.05</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>9881</t>
+          <t>5298</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>主营业务收入7</t>
+          <t>盈余公积12</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>主营业务收入</t>
+          <t>盈余公积</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>损益</t>
+          <t>权益</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>21716.94</v>
+        <v>40202.83</v>
       </c>
       <c r="F173" t="n">
-        <v>30296.27</v>
+        <v>18296.18</v>
       </c>
       <c r="G173" t="n">
-        <v>-8579.330000000002</v>
+        <v>21906.65</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>7879</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>短期借款10</t>
+          <t>长期借款13</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>短期借款</t>
+          <t>长期借款</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -5717,29 +5744,29 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>4506.27</v>
+        <v>23937.89</v>
       </c>
       <c r="F174" t="n">
-        <v>39860.02</v>
+        <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>-35353.75</v>
+        <v>23937.89</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>5039</t>
+          <t>7102</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>应付账款9</t>
+          <t>长期借款1</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>应付账款</t>
+          <t>长期借款</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -5748,258 +5775,137 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>4572.69</v>
+        <v>42503.99</v>
       </c>
       <c r="F175" t="n">
-        <v>17624.43</v>
+        <v>36221.28</v>
       </c>
       <c r="G175" t="n">
-        <v>-13051.74</v>
+        <v>6282.709999999999</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>9300</t>
+          <t>2905</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>长期借款10</t>
+          <t>主营业务成本4</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>长期借款</t>
+          <t>主营业务成本</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>负债</t>
+          <t>成本</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>18969.95</v>
+        <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>8565.190000000001</v>
+        <v>32337.81</v>
       </c>
       <c r="G176" t="n">
-        <v>10404.76</v>
+        <v>-32337.81</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>3895</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>管理费用10</t>
+          <t>应收账款2</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>管理费用</t>
+          <t>应收账款</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>成本</t>
-        </is>
+          <t>资产</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>24065.12</v>
       </c>
       <c r="F177" t="n">
-        <v>10403.28</v>
+        <v>49345.17</v>
       </c>
       <c r="G177" t="n">
-        <v>9286.300000000001</v>
+        <v>-25280.05</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>现金6</t>
+          <t>管理费用3</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>现金</t>
+          <t>管理费用</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>资产</t>
+          <t>成本</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>49990.93</v>
+        <v>15213.99</v>
       </c>
       <c r="F178" t="n">
-        <v>12609.69</v>
+        <v>45478.34</v>
       </c>
       <c r="G178" t="n">
-        <v>37381.24</v>
+        <v>-30264.35</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>2462</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>盈余公积15</t>
+          <t>应付账款3</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>盈余公积</t>
+          <t>应付账款</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>权益</t>
+          <t>负债</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>38241.47</v>
+        <v>32337.68</v>
       </c>
       <c r="F179" t="n">
-        <v>36871.84</v>
+        <v>43769.17</v>
       </c>
       <c r="G179" t="n">
-        <v>1369.630000000005</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>4610</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>应付账款13</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>应付账款</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>负债</t>
-        </is>
-      </c>
-      <c r="E180" t="n">
-        <v>16867.2</v>
-      </c>
-      <c r="F180" t="n">
-        <v>0</v>
-      </c>
-      <c r="G180" t="n">
-        <v>16867.2</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>5107</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>主营业务成本6</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>主营业务成本</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>成本</t>
-        </is>
-      </c>
-      <c r="E181" t="n">
-        <v>27934.4</v>
-      </c>
-      <c r="F181" t="n">
-        <v>0</v>
-      </c>
-      <c r="G181" t="n">
-        <v>27934.4</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>4436</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>应付账款12</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>应付账款</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>负债</t>
-        </is>
-      </c>
-      <c r="E182" t="n">
-        <v>10384.05</v>
-      </c>
-      <c r="F182" t="n">
-        <v>34483.67</v>
-      </c>
-      <c r="G182" t="n">
-        <v>-24099.62</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>2621</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>短期借款13</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>短期借款</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>负债</t>
-        </is>
-      </c>
-      <c r="E183" t="n">
-        <v>1785.01</v>
-      </c>
-      <c r="F183" t="n">
-        <v>6737.37</v>
-      </c>
-      <c r="G183" t="n">
-        <v>-4952.36</v>
+        <v>-11431.49</v>
       </c>
     </row>
   </sheetData>
